--- a/Cahier_de_Tests_YT_QuickView.xlsx
+++ b/Cahier_de_Tests_YT_QuickView.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dev\Chrome Extensions\YT-QuickView\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F82BF4-0F93-486C-AD37-297AE8D26B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1848E526-C4CC-4F42-96FF-4A97EB810FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1567AD5F-7A86-4577-B5C7-770DB6348DD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{1567AD5F-7A86-4577-B5C7-770DB6348DD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="6" r:id="rId1"/>
-    <sheet name="Navigation" sheetId="5" r:id="rId2"/>
+    <sheet name="Dates" sheetId="2" r:id="rId2"/>
     <sheet name="Emplacements" sheetId="4" r:id="rId3"/>
-    <sheet name="Vues" sheetId="3" r:id="rId4"/>
-    <sheet name="Dates" sheetId="2" r:id="rId5"/>
-    <sheet name="Mise en page" sheetId="1" r:id="rId6"/>
+    <sheet name="Mise en page" sheetId="1" r:id="rId4"/>
+    <sheet name="Navigation" sheetId="5" r:id="rId5"/>
+    <sheet name="Vues" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="150">
   <si>
     <t>ID</t>
   </si>
@@ -53,45 +53,24 @@
     <t>Résultat attendu</t>
   </si>
   <si>
-    <t>QV-01</t>
-  </si>
-  <si>
     <t>Apparition du bouton</t>
   </si>
   <si>
-    <t>QV-02</t>
-  </si>
-  <si>
     <t>Basculement de l'icône</t>
   </si>
   <si>
-    <t>QV-03</t>
-  </si>
-  <si>
     <t>Injection de classe</t>
   </si>
   <si>
-    <t>QV-04</t>
-  </si>
-  <si>
     <t>Persistance du choix</t>
   </si>
   <si>
-    <t>QV-05</t>
-  </si>
-  <si>
     <t>Désactivation page chaîne</t>
   </si>
   <si>
-    <t>QV-06</t>
-  </si>
-  <si>
     <t>Raccourci Clavier</t>
   </si>
   <si>
-    <t>QV-07</t>
-  </si>
-  <si>
     <t>Raccourci en saisie</t>
   </si>
   <si>
@@ -149,123 +128,72 @@
     <t>il y a 4 ans' / '4 years ago'</t>
   </si>
   <si>
-    <t>VW-01</t>
-  </si>
-  <si>
     <t>&lt; 1 000</t>
   </si>
   <si>
     <t>800 vues', '1 vue'</t>
   </si>
   <si>
-    <t>VW-02</t>
-  </si>
-  <si>
     <t>Milliers (Abrégé)</t>
   </si>
   <si>
     <t>12 k', '4,5 k'</t>
   </si>
   <si>
-    <t>VW-03</t>
-  </si>
-  <si>
     <t>Milliers (Complet)</t>
   </si>
   <si>
     <t>1 234 vues'</t>
   </si>
   <si>
-    <t>VW-04</t>
-  </si>
-  <si>
     <t>Millions (Abrégé)</t>
   </si>
   <si>
     <t>1,8 M'</t>
   </si>
   <si>
-    <t>VW-05</t>
-  </si>
-  <si>
     <t>Millions (Complet)</t>
   </si>
   <si>
     <t>1 800 000 vues'</t>
   </si>
   <si>
-    <t>VW-06</t>
-  </si>
-  <si>
     <t>Milliards</t>
   </si>
   <si>
     <t>1,2 Md', '1.2 B'</t>
   </si>
   <si>
-    <t>CX-01</t>
-  </si>
-  <si>
     <t>Accueil</t>
   </si>
   <si>
-    <t>CX-02</t>
-  </si>
-  <si>
     <t>Page de chaîne</t>
   </si>
   <si>
-    <t>CX-03</t>
-  </si>
-  <si>
     <t>Lecture vidéo</t>
   </si>
   <si>
-    <t>CX-04</t>
-  </si>
-  <si>
     <t>Videowall</t>
   </si>
   <si>
-    <t>CX-05</t>
-  </si>
-  <si>
     <t>Onglet Communauté</t>
   </si>
   <si>
-    <t>CX-06</t>
-  </si>
-  <si>
     <t>Shorts</t>
   </si>
   <si>
-    <t>CX-07</t>
-  </si>
-  <si>
     <t>Commentaires</t>
   </si>
   <si>
-    <t>CX-08</t>
-  </si>
-  <si>
     <t>Marqueur YouTube</t>
   </si>
   <si>
-    <t>DY-01</t>
-  </si>
-  <si>
     <t>Navigation SPA</t>
   </si>
   <si>
-    <t>DY-02</t>
-  </si>
-  <si>
     <t>Scroll Infini</t>
   </si>
   <si>
-    <t>DY-03</t>
-  </si>
-  <si>
     <t>Thème Natif</t>
   </si>
   <si>
@@ -392,9 +320,6 @@
     <t>Faire défiler les comms</t>
   </si>
   <si>
-    <t>Badge 'Nouveau' / 'En direct'</t>
-  </si>
-  <si>
     <t>Vues/Dates colorisées</t>
   </si>
   <si>
@@ -416,9 +341,6 @@
     <t>Ancienneté colorisée</t>
   </si>
   <si>
-    <t>Couleur youtube-marker</t>
-  </si>
-  <si>
     <t>Naviguer sans F5</t>
   </si>
   <si>
@@ -465,6 +387,108 @@
   </si>
   <si>
     <t>f6=40000000 forcé (pas de liste)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>EM-01</t>
+  </si>
+  <si>
+    <t>EM-02</t>
+  </si>
+  <si>
+    <t>EM-03</t>
+  </si>
+  <si>
+    <t>EM-04</t>
+  </si>
+  <si>
+    <t>EM-05</t>
+  </si>
+  <si>
+    <t>EM-06</t>
+  </si>
+  <si>
+    <t>EM-07</t>
+  </si>
+  <si>
+    <t>EM-08</t>
+  </si>
+  <si>
+    <t>MP-01</t>
+  </si>
+  <si>
+    <t>MP-02</t>
+  </si>
+  <si>
+    <t>MP-03</t>
+  </si>
+  <si>
+    <t>MP-05</t>
+  </si>
+  <si>
+    <t>MP-06</t>
+  </si>
+  <si>
+    <t>MP-07</t>
+  </si>
+  <si>
+    <t>MP-04</t>
+  </si>
+  <si>
+    <t>NV-01</t>
+  </si>
+  <si>
+    <t>NV-02</t>
+  </si>
+  <si>
+    <t>NV-03</t>
+  </si>
+  <si>
+    <t>VU-01</t>
+  </si>
+  <si>
+    <t>VU-02</t>
+  </si>
+  <si>
+    <t>VU-03</t>
+  </si>
+  <si>
+    <t>VU-04</t>
+  </si>
+  <si>
+    <t>VU-05</t>
+  </si>
+  <si>
+    <t>VU-06</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Forcé</t>
+  </si>
+  <si>
+    <t>Partout</t>
+  </si>
+  <si>
+    <t>Marqueur colorisé</t>
+  </si>
+  <si>
+    <t>DT-07</t>
+  </si>
+  <si>
+    <t>Changer langue</t>
+  </si>
+  <si>
+    <t>Tout</t>
+  </si>
+  <si>
+    <t>Colorisation correcte</t>
+  </si>
+  <si>
+    <t>VU-07</t>
   </si>
 </sst>
 </file>
@@ -488,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +522,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -538,6 +568,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -854,17 +893,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F442A6A-3BBC-4BA2-9520-BE427F3044DD}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,83 +919,119 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -962,18 +1039,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328BE97-9F18-475D-A5BA-27688899643D}">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B6A403-1406-4625-BE7C-70323470149E}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -987,53 +1066,161 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>126</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>128</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1042,17 +1229,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5027913-92B1-4519-9CCA-42C54248269A}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,128 +1255,182 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1195,18 +1438,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C26DB4B-7745-4C4D-8D50-D6886E765733}">
-  <dimension ref="A1:E7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B51DE63-CB96-4CC7-B9EF-178872F7C8DF}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1220,98 +1465,161 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1319,18 +1627,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B6A403-1406-4625-BE7C-70323470149E}">
-  <dimension ref="A1:E7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328BE97-9F18-475D-A5BA-27688899643D}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1344,98 +1654,77 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1443,18 +1732,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B51DE63-CB96-4CC7-B9EF-178872F7C8DF}">
-  <dimension ref="A1:E8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C26DB4B-7745-4C4D-8D50-D6886E765733}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1468,113 +1759,161 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>88</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>35</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
